--- a/kobe_spots.xlsx
+++ b/kobe_spots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kuan Yu\Desktop\kobe-tourism-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA5A67E-8AB2-46FA-B827-C0C3BFC46C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1631245C-4079-47D4-8A8C-120E5F90538A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="136">
   <si>
     <t>spot_name</t>
   </si>
@@ -455,7 +455,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
-    <numFmt numFmtId="181" formatCode="#,##0_);[Red]\(#,##0\)"/>
+    <numFmt numFmtId="177" formatCode="#,##0_);[Red]\(#,##0\)"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -533,13 +533,13 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -822,7 +822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H297"/>
+  <dimension ref="A1:H296"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="49.796875" style="5" customWidth="1"/>
@@ -3020,22 +3020,22 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C85" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="E85" s="9">
-        <v>4.0999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F85" s="12">
-        <v>783</v>
+        <v>349</v>
       </c>
       <c r="G85" s="4">
         <v>46176</v>
@@ -3046,7 +3046,7 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>31</v>
@@ -3055,13 +3055,13 @@
         <v>4</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="E86" s="9">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="F86" s="12">
-        <v>349</v>
+        <v>774</v>
       </c>
       <c r="G86" s="4">
         <v>46176</v>
@@ -3072,7 +3072,7 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>31</v>
@@ -3084,10 +3084,10 @@
         <v>7</v>
       </c>
       <c r="E87" s="9">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="F87" s="12">
-        <v>774</v>
+        <v>205</v>
       </c>
       <c r="G87" s="4">
         <v>46176</v>
@@ -3098,22 +3098,22 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="C88" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="E88" s="9">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="F88" s="12">
-        <v>205</v>
+        <v>147</v>
       </c>
       <c r="G88" s="4">
         <v>46176</v>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>48</v>
@@ -3136,10 +3136,10 @@
         <v>27</v>
       </c>
       <c r="E89" s="9">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="F89" s="12">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="G89" s="4">
         <v>46176</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>48</v>
@@ -3159,13 +3159,13 @@
         <v>8</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="E90" s="9">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="F90" s="12">
-        <v>131</v>
+        <v>188</v>
       </c>
       <c r="G90" s="4">
         <v>46176</v>
@@ -3176,22 +3176,22 @@
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C91" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="E91" s="9">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="F91" s="12">
-        <v>188</v>
+        <v>364</v>
       </c>
       <c r="G91" s="4">
         <v>46176</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>28</v>
@@ -3214,10 +3214,10 @@
         <v>80</v>
       </c>
       <c r="E92" s="9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="F92" s="12">
-        <v>364</v>
+        <v>149</v>
       </c>
       <c r="G92" s="4">
         <v>46176</v>
@@ -3228,7 +3228,7 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>28</v>
@@ -3237,13 +3237,13 @@
         <v>2</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="E93" s="9">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="F93" s="12">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="G93" s="4">
         <v>46176</v>
@@ -3254,7 +3254,7 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>28</v>
@@ -3266,10 +3266,10 @@
         <v>27</v>
       </c>
       <c r="E94" s="9">
-        <v>3.9</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F94" s="12">
-        <v>126</v>
+        <v>1191</v>
       </c>
       <c r="G94" s="4">
         <v>46176</v>
@@ -3280,7 +3280,7 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>28</v>
@@ -3289,13 +3289,13 @@
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="E95" s="9">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="F95" s="12">
-        <v>1191</v>
+        <v>168</v>
       </c>
       <c r="G95" s="4">
         <v>46176</v>
@@ -3306,7 +3306,7 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>28</v>
@@ -3315,13 +3315,13 @@
         <v>2</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="E96" s="9">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="F96" s="12">
-        <v>168</v>
+        <v>223</v>
       </c>
       <c r="G96" s="4">
         <v>46176</v>
@@ -3332,7 +3332,7 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>28</v>
@@ -3341,13 +3341,13 @@
         <v>2</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="E97" s="9">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="F97" s="12">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="G97" s="4">
         <v>46176</v>
@@ -3358,7 +3358,7 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>28</v>
@@ -3367,13 +3367,13 @@
         <v>2</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="E98" s="9">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="F98" s="12">
-        <v>213</v>
+        <v>132</v>
       </c>
       <c r="G98" s="4">
         <v>46176</v>
@@ -3384,22 +3384,22 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="C99" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="E99" s="9">
-        <v>3.8</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F99" s="12">
-        <v>132</v>
+        <v>4305</v>
       </c>
       <c r="G99" s="4">
         <v>46176</v>
@@ -3410,7 +3410,7 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>4</v>
@@ -3422,10 +3422,10 @@
         <v>130</v>
       </c>
       <c r="E100" s="9">
-        <v>4.4000000000000004</v>
+        <v>3.9</v>
       </c>
       <c r="F100" s="12">
-        <v>4305</v>
+        <v>448</v>
       </c>
       <c r="G100" s="4">
         <v>46176</v>
@@ -3436,7 +3436,7 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>4</v>
@@ -3445,13 +3445,13 @@
         <v>1</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="E101" s="9">
-        <v>3.9</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F101" s="12">
-        <v>448</v>
+        <v>5157</v>
       </c>
       <c r="G101" s="4">
         <v>46176</v>
@@ -3461,30 +3461,14 @@
       </c>
     </row>
     <row r="102" spans="1:8">
-      <c r="A102" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C102" s="1">
-        <v>1</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E102" s="9">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="F102" s="12">
-        <v>5157</v>
-      </c>
-      <c r="G102" s="4">
-        <v>46176</v>
-      </c>
-      <c r="H102" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="A102" s="1"/>
+      <c r="B102" s="1"/>
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="9"/>
+      <c r="F102" s="12"/>
+      <c r="G102" s="4"/>
+      <c r="H102" s="1"/>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1"/>
@@ -5426,16 +5410,6 @@
       <c r="G296" s="4"/>
       <c r="H296" s="1"/>
     </row>
-    <row r="297" spans="1:8">
-      <c r="A297" s="1"/>
-      <c r="B297" s="1"/>
-      <c r="C297" s="1"/>
-      <c r="D297" s="1"/>
-      <c r="E297" s="9"/>
-      <c r="F297" s="12"/>
-      <c r="G297" s="4"/>
-      <c r="H297" s="1"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
